--- a/results/Int All Data 0.8/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.8/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>0.0009808013050334676</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00104962561221144</v>
+        <v>0.001081287881340726</v>
       </c>
       <c r="F3" t="n">
         <v>0.001269702013429213</v>
@@ -1694,13 +1694,13 @@
         <v>-0.001190917126655706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005510263311408805</v>
+        <v>0.005415276504020941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00398676159425923</v>
+        <v>0.003981484549404349</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00355468732858535</v>
+        <v>0.003565285600774275</v>
       </c>
       <c r="K3" t="n">
         <v>0.0009991249973371305</v>
@@ -1712,10 +1712,10 @@
         <v>-0.0001432511736349984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003893733704438968</v>
+        <v>0.003867348480164558</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001430923229477955</v>
+        <v>0.001399260960348665</v>
       </c>
       <c r="P3" t="n">
         <v>-0.0005273236929600499</v>
@@ -1724,7 +1724,7 @@
         <v>0.0074764587364043</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005220947910153961</v>
+        <v>0.0002213032342871635</v>
       </c>
       <c r="S3" t="n">
         <v>0.007393421657074448</v>
@@ -1736,7 +1736,7 @@
         <v>0.01213946583960614</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00398676159425923</v>
+        <v>0.004002592728823874</v>
       </c>
       <c r="W3" t="n">
         <v>0.005971863156168903</v>
@@ -1751,7 +1751,7 @@
         <v>0.0003708578438965914</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.00298375194002604</v>
+        <v>-0.002989028984880922</v>
       </c>
       <c r="AB3" t="n">
         <v>8.023895245674816e-05</v>
@@ -1763,10 +1763,10 @@
         <v>-0.001021880061395142</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004278060934411862</v>
+        <v>0.004288615024121624</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0006853188391696184</v>
+        <v>-0.0007271697445093871</v>
       </c>
       <c r="AG3" t="n">
         <v>0.001152905533835695</v>
@@ -1778,10 +1778,10 @@
         <v>0.005324332091653528</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.006654269280024032</v>
+        <v>0.006669734961089394</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01766307143502664</v>
+        <v>0.01762613212104246</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01347712687754078</v>
@@ -1790,7 +1790,7 @@
         <v>0.01430398974989993</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0001947461158808517</v>
+        <v>-0.0001630838467515616</v>
       </c>
       <c r="AO3" t="n">
         <v>0.08778273348706279</v>
@@ -1802,7 +1802,7 @@
         <v>0.02293285329879571</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.004278060934411862</v>
+        <v>0.004278060934411863</v>
       </c>
       <c r="AS3" t="n">
         <v>-0.0006863839339094346</v>
@@ -1817,7 +1817,7 @@
         <v>0.00161061152665115</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0003411652094964745</v>
+        <v>0.0002820213555949347</v>
       </c>
       <c r="AX3" t="n">
         <v>9.747773678951522e-05</v>
@@ -1826,13 +1826,13 @@
         <v>0.06981871718236943</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.386959103844899e-06</v>
+        <v>-1.244417546079845e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.00193208283584564</v>
+        <v>0.001953191015265164</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.000279447566760317</v>
+        <v>0.0003955425535677048</v>
       </c>
       <c r="BC3" t="n">
         <v>0.0001689538910955258</v>
@@ -1844,7 +1844,7 @@
         <v>0.002695991503611107</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.001209593065371847</v>
+        <v>-0.001167376706532797</v>
       </c>
       <c r="BG3" t="n">
         <v>0.000772682809047066</v>
@@ -1856,7 +1856,7 @@
         <v>0.1480210305166843</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.049165240917485e-05</v>
+        <v>-3.560333439821435e-05</v>
       </c>
       <c r="BK3" t="n">
         <v>0.07208967032362272</v>
@@ -1868,7 +1868,7 @@
         <v>0.009071854277247569</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.00193208283584564</v>
+        <v>0.001932082835845637</v>
       </c>
       <c r="BO3" t="n">
         <v>0.01881831102151744</v>
@@ -1883,7 +1883,7 @@
         <v>0.02496656918264399</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.00232382960970938</v>
+        <v>0.002619709575082012</v>
       </c>
       <c r="BT3" t="n">
         <v>0.0001789810852406459</v>
@@ -1892,28 +1892,28 @@
         <v>0.009403608692912301</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01537783017159756</v>
+        <v>0.01611729919852362</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0001388391475686412</v>
+        <v>0.0001441161924235224</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.01146507914528762</v>
+        <v>0.01128038257536678</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.000533066627379052</v>
+        <v>0.0005436207170888154</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0005277218919434558</v>
+        <v>0.0005119584479595286</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0003317322189763707</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.003342120511589794</v>
+        <v>0.003426187775768615</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.00438805145937032</v>
+        <v>0.004293811703513117</v>
       </c>
       <c r="CD3" t="n">
         <v>0.003856943932440669</v>
@@ -1922,7 +1922,7 @@
         <v>0.001598216246252691</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0006675818446252301</v>
+        <v>-7.628259875120374e-05</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4536566683843103</v>
@@ -1934,7 +1934,7 @@
         <v>0.3859705823795003</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0001441161924235224</v>
+        <v>0.0001388391475686412</v>
       </c>
       <c r="CK3" t="n">
         <v>0.001002561993951844</v>
@@ -1949,7 +1949,7 @@
         <v>0.009498152467414138</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.02144529180001849</v>
+        <v>0.02140835248603432</v>
       </c>
       <c r="CP3" t="n">
         <v>-0.0001113008320850595</v>
@@ -1958,13 +1958,13 @@
         <v>0.0510015676220801</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01791033604322615</v>
+        <v>0.01791561308808103</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.3264594805288533</v>
+        <v>0.3264858657531277</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.05608644707135919</v>
+        <v>0.05593868981542251</v>
       </c>
       <c r="CU3" t="n">
         <v>0.01027234084170527</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.001954810229792488</v>
+        <v>0.001997026588631537</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.003577564502794652</v>
+        <v>0.003535348143955601</v>
       </c>
       <c r="CZ3" t="n">
         <v>0.0004484586686401904</v>
@@ -1988,7 +1988,7 @@
         <v>-0.0001658322474558371</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.02076225272961765</v>
+        <v>0.0208044690884567</v>
       </c>
       <c r="DC3" t="n">
         <v>0.3604883186301104</v>
@@ -2000,7 +2000,7 @@
         <v>0.08076634456513056</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.3264594805288533</v>
+        <v>0.3264489264391436</v>
       </c>
       <c r="DG3" t="n">
         <v>0.005386111241553439</v>
@@ -2015,7 +2015,7 @@
         <v>0.001087924573785031</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.00448139229407972</v>
+        <v>0.004491946383789482</v>
       </c>
       <c r="DL3" t="n">
         <v>-0.0001696675764194466</v>
@@ -2027,10 +2027,10 @@
         <v>0.001900800072361881</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.009660540925771134</v>
+        <v>0.009723933154610426</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.002057365287616076</v>
+        <v>0.002036257108196552</v>
       </c>
       <c r="DQ3" t="n">
         <v>-6.690576142486693e-05</v>
@@ -2042,10 +2042,10 @@
         <v>0.0008257682359440043</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.01574101060552665</v>
+        <v>0.015741076602961</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.01699502110385114</v>
+        <v>0.01698446701414138</v>
       </c>
       <c r="DV3" t="n">
         <v>0.0006519668417258773</v>
@@ -2066,7 +2066,7 @@
         <v>0.003319081617772347</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.009665885661206731</v>
+        <v>0.009634155701496729</v>
       </c>
       <c r="EC3" t="n">
         <v>0.01623300372291694</v>
@@ -2081,7 +2081,7 @@
         <v>0.0004743348646654355</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.00153395759814451</v>
+        <v>0.001518126463579866</v>
       </c>
       <c r="EH3" t="n">
         <v>0.0001436749903939838</v>
@@ -2090,19 +2090,19 @@
         <v>0.005619153631399107</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.002433426273082184</v>
+        <v>0.002491473766485879</v>
       </c>
       <c r="EK3" t="n">
         <v>0.001348130893547033</v>
       </c>
       <c r="EL3" t="n">
-        <v>4.719888284971385e-05</v>
+        <v>5.247592770459498e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0.000190123506929355</v>
+        <v>-0.0001690153275098305</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0.000190123506929355</v>
+        <v>-0.0002217857760586428</v>
       </c>
       <c r="EO3" t="n">
         <v>0.0002834462563379258</v>
@@ -2111,7 +2111,7 @@
         <v>5.129807560960376e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.00131050659902638</v>
+        <v>0.001358000002720312</v>
       </c>
       <c r="ER3" t="n">
         <v>0.0001558041896907003</v>
@@ -2120,7 +2120,7 @@
         <v>0.0003250447765581488</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.002387742027715241</v>
+        <v>0.002313863399746902</v>
       </c>
       <c r="EU3" t="n">
         <v>0.004147793735407075</v>
@@ -2132,7 +2132,7 @@
         <v>0.006805967954863287</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.001348130893547033</v>
+        <v>0.001342853848692151</v>
       </c>
       <c r="EY3" t="n">
         <v>-0.0006930717631364424</v>
@@ -2154,7 +2154,7 @@
         <v>0.003445223751996922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005643015293668032</v>
+        <v>0.005654783922359798</v>
       </c>
       <c r="F4" t="n">
         <v>0.002416178109564379</v>
@@ -2163,13 +2163,13 @@
         <v>0.003899265370811189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01061740295133947</v>
+        <v>0.01073919881691976</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0110317182320776</v>
+        <v>0.01103370940853814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004936965141386427</v>
+        <v>0.004931535056272745</v>
       </c>
       <c r="K4" t="n">
         <v>0.002485216798992968</v>
@@ -2181,10 +2181,10 @@
         <v>0.0004670032211364249</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007867724206805368</v>
+        <v>0.007877949689820455</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004872914279501198</v>
+        <v>0.004875129550561786</v>
       </c>
       <c r="P4" t="n">
         <v>0.003956824515864893</v>
@@ -2193,7 +2193,7 @@
         <v>0.01476065919823021</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001892607808868584</v>
+        <v>0.002405842017429399</v>
       </c>
       <c r="S4" t="n">
         <v>0.01829283159713845</v>
@@ -2205,7 +2205,7 @@
         <v>0.01298722633542339</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0110317182320776</v>
+        <v>0.01102589408328921</v>
       </c>
       <c r="W4" t="n">
         <v>0.01177509691489022</v>
@@ -2220,7 +2220,7 @@
         <v>0.002066650090906791</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00604887450519672</v>
+        <v>0.006060112842557953</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0003661281064293654</v>
@@ -2232,10 +2232,10 @@
         <v>0.003982294960528245</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.008815170061978721</v>
+        <v>0.008811787921745197</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004814808921147166</v>
+        <v>0.004926210842687845</v>
       </c>
       <c r="AG4" t="n">
         <v>0.002426576709809756</v>
@@ -2247,10 +2247,10 @@
         <v>0.005887428070980234</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006824747746400533</v>
+        <v>0.006835360311685458</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01517669809590605</v>
+        <v>0.01520092053075067</v>
       </c>
       <c r="AL4" t="n">
         <v>0.01223900497503522</v>
@@ -2259,7 +2259,7 @@
         <v>0.01528987523244569</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001868414652269249</v>
+        <v>0.001890531175089086</v>
       </c>
       <c r="AO4" t="n">
         <v>0.03513671148369182</v>
@@ -2286,7 +2286,7 @@
         <v>0.002746275478125048</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003677171515243783</v>
+        <v>0.003609004310649282</v>
       </c>
       <c r="AX4" t="n">
         <v>0.0004049855176992829</v>
@@ -2295,13 +2295,13 @@
         <v>0.0943611407884658</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0003272184295351689</v>
+        <v>0.0003283912649836413</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.007371832438162324</v>
+        <v>0.007360774836900726</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005597937076117947</v>
+        <v>0.005603533314680602</v>
       </c>
       <c r="BC4" t="n">
         <v>0.002998793434092963</v>
@@ -2313,7 +2313,7 @@
         <v>0.004959950436303484</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.005055823841248749</v>
+        <v>0.005083421314240152</v>
       </c>
       <c r="BG4" t="n">
         <v>0.002220957223754539</v>
@@ -2325,7 +2325,7 @@
         <v>0.05864585844784738</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004265961279718649</v>
+        <v>0.004249054002575436</v>
       </c>
       <c r="BK4" t="n">
         <v>0.05886999097483996</v>
@@ -2337,7 +2337,7 @@
         <v>0.01286713134624173</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.007371832438162324</v>
+        <v>0.007371832438162325</v>
       </c>
       <c r="BO4" t="n">
         <v>0.02187881124982344</v>
@@ -2352,7 +2352,7 @@
         <v>0.03005002151432317</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01202022028884131</v>
+        <v>0.0118798489446933</v>
       </c>
       <c r="BT4" t="n">
         <v>0.00135251242828274</v>
@@ -2361,28 +2361,28 @@
         <v>0.0124779718761793</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01842779848854218</v>
+        <v>0.01758898774111198</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.00030160567678925</v>
+        <v>0.0003044839169029962</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01247227746030311</v>
+        <v>0.01261044890776959</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002372138622634683</v>
+        <v>0.002371564211991953</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002383674426805441</v>
+        <v>0.002374694641498058</v>
       </c>
       <c r="CA4" t="n">
         <v>0.005354588364151835</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01340156367953627</v>
+        <v>0.01336582658152123</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01454817330406748</v>
+        <v>0.01464034107914915</v>
       </c>
       <c r="CD4" t="n">
         <v>0.00715945811868417</v>
@@ -2391,7 +2391,7 @@
         <v>0.004225769630530747</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003132281620867611</v>
+        <v>0.003576786737897397</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1115526452069126</v>
@@ -2403,7 +2403,7 @@
         <v>0.1003762213737665</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0003044839169029962</v>
+        <v>0.00030160567678925</v>
       </c>
       <c r="CK4" t="n">
         <v>0.002177529950505213</v>
@@ -2418,7 +2418,7 @@
         <v>0.01770998891559968</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.03963398148864909</v>
+        <v>0.03965072946604488</v>
       </c>
       <c r="CP4" t="n">
         <v>0.0006399108390682487</v>
@@ -2427,13 +2427,13 @@
         <v>0.04641733444982105</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.01979760807487548</v>
+        <v>0.01979188786627071</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1259667955910601</v>
+        <v>0.1259738676320284</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.03636056446561241</v>
+        <v>0.03645299952014021</v>
       </c>
       <c r="CU4" t="n">
         <v>0.01644914602127207</v>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.006105279919157496</v>
+        <v>0.006075837583548885</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.008939820171873799</v>
+        <v>0.008977230770102042</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.001350690913188039</v>
@@ -2457,7 +2457,7 @@
         <v>0.0007625100795664316</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.02733213630927073</v>
+        <v>0.02740071184006625</v>
       </c>
       <c r="DC4" t="n">
         <v>0.08636373165008811</v>
@@ -2469,7 +2469,7 @@
         <v>0.04078651039084528</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1259667955910601</v>
+        <v>0.1259639821385919</v>
       </c>
       <c r="DG4" t="n">
         <v>0.01219253195198362</v>
@@ -2484,7 +2484,7 @@
         <v>0.002256959726135818</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.01162703295342366</v>
+        <v>0.0116235717455005</v>
       </c>
       <c r="DL4" t="n">
         <v>0.0005215673542592264</v>
@@ -2496,10 +2496,10 @@
         <v>0.003918320317663473</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01578646693695117</v>
+        <v>0.0157693557716902</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.005134961080463457</v>
+        <v>0.005153195276632727</v>
       </c>
       <c r="DQ4" t="n">
         <v>0.0001546493199018081</v>
@@ -2511,10 +2511,10 @@
         <v>0.00259651450939468</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0304167002388061</v>
+        <v>0.03041645384967376</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.03522395169896263</v>
+        <v>0.03522920346501445</v>
       </c>
       <c r="DV4" t="n">
         <v>0.002099507580746819</v>
@@ -2535,7 +2535,7 @@
         <v>0.007738662617333675</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0157959280063842</v>
+        <v>0.0157992328084317</v>
       </c>
       <c r="EC4" t="n">
         <v>0.02247740498588774</v>
@@ -2550,7 +2550,7 @@
         <v>0.001283413610460895</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.004574135575577446</v>
+        <v>0.004578682753555326</v>
       </c>
       <c r="EH4" t="n">
         <v>0.0004988059658786583</v>
@@ -2559,19 +2559,19 @@
         <v>0.009197526343287804</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.005936283960900137</v>
+        <v>0.005922988404123728</v>
       </c>
       <c r="EK4" t="n">
         <v>0.002738516348976378</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001746546233867507</v>
+        <v>0.0001738655205136632</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0005609309400067701</v>
+        <v>0.0005596117996700086</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0005609309400067701</v>
+        <v>0.0005775543875580854</v>
       </c>
       <c r="EO4" t="n">
         <v>0.0003508314276720807</v>
@@ -2580,7 +2580,7 @@
         <v>0.0001974609873749478</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.003849974786007626</v>
+        <v>0.003839266425712824</v>
       </c>
       <c r="ER4" t="n">
         <v>0.001127607198324949</v>
@@ -2589,7 +2589,7 @@
         <v>0.0008555510666380191</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.005849996913881295</v>
+        <v>0.005874048297510988</v>
       </c>
       <c r="EU4" t="n">
         <v>0.008093372676792552</v>
@@ -2601,7 +2601,7 @@
         <v>0.01275396754274079</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.002738516348976378</v>
+        <v>0.002742016341166654</v>
       </c>
       <c r="EY4" t="n">
         <v>0.001614028133799135</v>
@@ -2662,7 +2662,7 @@
         <v>-0.002993051843933725</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00235168359166219</v>
+        <v>-0.004432717678100251</v>
       </c>
       <c r="S5" t="n">
         <v>-0.003856175091193304</v>
@@ -2689,7 +2689,7 @@
         <v>-0.003113456464379949</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01456464379947226</v>
+        <v>-0.01461741424802108</v>
       </c>
       <c r="AB5" t="n">
         <v>-0.0002455795677799744</v>
@@ -2704,7 +2704,7 @@
         <v>-0.00080171031533941</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01377308707124009</v>
+        <v>-0.01414248021108178</v>
       </c>
       <c r="AG5" t="n">
         <v>-0.002585751978891826</v>
@@ -2830,7 +2830,7 @@
         <v>-0.001055408970976246</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.007176781002638499</v>
+        <v>-0.004115446285408863</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.0001068376068376065</v>
@@ -2842,7 +2842,7 @@
         <v>-0.004061998931052901</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004115446285408863</v>
+        <v>-0.004061998931052901</v>
       </c>
       <c r="CA5" t="n">
         <v>-0.008017103153393889</v>
@@ -2968,7 +2968,7 @@
         <v>-0.005932656333511466</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.001846965699208447</v>
+        <v>-0.002058047493403692</v>
       </c>
       <c r="DQ5" t="n">
         <v>-0.0003438113948919796</v>
@@ -3070,7 +3070,7 @@
         <v>-0.002374670184696559</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0003126628452318813</v>
+        <v>-0.0003166226912928672</v>
       </c>
       <c r="EY5" t="n">
         <v>-0.003543512245961433</v>
@@ -3104,7 +3104,7 @@
         <v>0.001685845466312083</v>
       </c>
       <c r="I6" t="n">
-        <v>2.450369086844095e-05</v>
+        <v>1.131107873123815e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.001721049952599346</v>
@@ -3143,7 +3143,7 @@
         <v>0.002927842442645068</v>
       </c>
       <c r="V6" t="n">
-        <v>2.450369086844095e-05</v>
+        <v>6.408152728004933e-05</v>
       </c>
       <c r="W6" t="n">
         <v>-0.001250159459114678</v>
@@ -3173,7 +3173,7 @@
         <v>0.0007831069664758217</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0003315324165029637</v>
+        <v>-0.0003683693516699615</v>
       </c>
       <c r="AG6" t="n">
         <v>5.344735435595383e-05</v>
@@ -3188,7 +3188,7 @@
         <v>-0.0001007914487392098</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.009171006341711821</v>
+        <v>0.008893961486830538</v>
       </c>
       <c r="AL6" t="n">
         <v>0.009729619849636783</v>
@@ -3233,13 +3233,13 @@
         <v>0.01537668158878166</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0002248784695985134</v>
+        <v>-0.0002267057370949149</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.001186827412992911</v>
+        <v>-0.001028516067346477</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0006410256410256387</v>
+        <v>-0.0006287466626366478</v>
       </c>
       <c r="BC6" t="n">
         <v>2.672367717798108e-05</v>
@@ -3263,7 +3263,7 @@
         <v>0.09270443613041154</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.01282051281882e-05</v>
+        <v>-1.665334536937735e-17</v>
       </c>
       <c r="BK6" t="n">
         <v>0.02446923255315332</v>
@@ -3275,7 +3275,7 @@
         <v>0.0009744170648627454</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001186827412992911</v>
+        <v>-0.001186827412992927</v>
       </c>
       <c r="BO6" t="n">
         <v>0.004057852658771472</v>
@@ -3290,7 +3290,7 @@
         <v>0.007368640526115158</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001725277246406792</v>
+        <v>-0.001418989845058088</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.0002095941776785015</v>
@@ -3299,25 +3299,25 @@
         <v>0.0004407051282051266</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001531950990660727</v>
+        <v>-0.0007401315789473673</v>
       </c>
       <c r="BW6" t="n">
         <v>-4.008551576697717e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.004798904280269712</v>
+        <v>0.003413680005863384</v>
       </c>
       <c r="BY6" t="n">
         <v>0.000233572633906487</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.000233572633906487</v>
+        <v>0.000173558070638341</v>
       </c>
       <c r="CA6" t="n">
         <v>-0.001348881888199097</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.001644736842105268</v>
+        <v>-0.001345646437994702</v>
       </c>
       <c r="CC6" t="n">
         <v>-0.001658374792703143</v>
@@ -3329,7 +3329,7 @@
         <v>-0.002029971631788835</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0009932089771021585</v>
+        <v>-0.0002748114560081283</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3626320835515405</v>
@@ -3371,7 +3371,7 @@
         <v>0.2656613224678511</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.03407668637684758</v>
+        <v>0.03370729323700589</v>
       </c>
       <c r="CU6" t="n">
         <v>0.002668270899875014</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.001883671674474535</v>
+        <v>-0.001567048983181668</v>
       </c>
       <c r="CY6" t="n">
         <v>-0.001145838794940718</v>
@@ -3506,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0005200963462599046</v>
+        <v>-0.0004673258977110934</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0005200963462599046</v>
+        <v>-0.0006219142614182049</v>
       </c>
       <c r="EO6" t="n">
         <v>1.370614035087758e-05</v>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002257945373773396</v>
+        <v>0.00230531161975997</v>
       </c>
       <c r="F7" t="n">
         <v>0.001145238850137398</v>
@@ -3588,10 +3588,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009621927510068241</v>
+        <v>0.0008302666296347794</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000841618698761526</v>
+        <v>0.0006886092506145248</v>
       </c>
       <c r="P7" t="n">
         <v>0.0002638522427440726</v>
@@ -3639,7 +3639,7 @@
         <v>-0.0007172078430055074</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0016575801888292</v>
+        <v>0.001710350637378011</v>
       </c>
       <c r="AF7" t="n">
         <v>0.0005247338901302578</v>
@@ -3678,7 +3678,7 @@
         <v>0.02410227881389819</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0016575801888292</v>
+        <v>0.001657580188829205</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3702,13 +3702,13 @@
         <v>0.01897796408371346</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-2.741228070174961e-05</v>
+        <v>-7.652819425775226e-05</v>
       </c>
       <c r="BA7" t="n">
         <v>0.001811854190585527</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0005497099744673106</v>
+        <v>0.001105626951726268</v>
       </c>
       <c r="BC7" t="n">
         <v>0.0004318649844959165</v>
@@ -3732,7 +3732,7 @@
         <v>0.1583007711369858</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0007282030276995199</v>
+        <v>0.0004366522090402669</v>
       </c>
       <c r="BK7" t="n">
         <v>0.06915295760645725</v>
@@ -3777,10 +3777,10 @@
         <v>0.00916881452361528</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003654194614870931</v>
+        <v>0.0004181899100359099</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0003654194614870931</v>
+        <v>0.0003189207909581826</v>
       </c>
       <c r="CA7" t="n">
         <v>-0.0001031156133655731</v>
@@ -3798,7 +3798,7 @@
         <v>0.001006730071196899</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0001546676544635972</v>
+        <v>0.000527945113788475</v>
       </c>
       <c r="CG7" t="n">
         <v>0.4858712130293086</v>
@@ -3825,7 +3825,7 @@
         <v>0.003360460310900609</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.007950540475983342</v>
+        <v>0.007765843906062503</v>
       </c>
       <c r="CP7" t="n">
         <v>-0.0002054473361719489</v>
@@ -3903,7 +3903,7 @@
         <v>0.001015214223391686</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.002623673004711946</v>
+        <v>0.002663851446699633</v>
       </c>
       <c r="DP7" t="n">
         <v>-0.0001603420630678864</v>
@@ -3918,10 +3918,10 @@
         <v>0.001118085099947547</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.001829896483698834</v>
+        <v>0.001803841246596177</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.001114271571789416</v>
+        <v>0.001061501123240593</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
         <v>0.0001964636542239495</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.002623673004711946</v>
+        <v>0.002491746883339918</v>
       </c>
       <c r="EC7" t="n">
         <v>0.009270432192666267</v>
@@ -3996,7 +3996,7 @@
         <v>2.670940170940161e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0002484338917037088</v>
+        <v>0.0001593384020737831</v>
       </c>
       <c r="EU7" t="n">
         <v>0.001849627497130846</v>
@@ -4030,7 +4030,7 @@
         <v>0.001031326782171352</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003436707355738741</v>
+        <v>0.003492179905568671</v>
       </c>
       <c r="F8" t="n">
         <v>0.001906817122484372</v>
@@ -4060,7 +4060,7 @@
         <v>0.004756998953427485</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005376863655148301</v>
+        <v>0.005374212706398577</v>
       </c>
       <c r="P8" t="n">
         <v>0.0009274580317240461</v>
@@ -4123,7 +4123,7 @@
         <v>0.005505749300501355</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.01295816511428299</v>
+        <v>0.0129845503385574</v>
       </c>
       <c r="AK8" t="n">
         <v>0.01839179994244126</v>
@@ -4135,7 +4135,7 @@
         <v>0.01502822889634433</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0008114252071471401</v>
+        <v>0.001048826590730556</v>
       </c>
       <c r="AO8" t="n">
         <v>0.1008676415669668</v>
@@ -4162,7 +4162,7 @@
         <v>0.003263023149975058</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003230802004328259</v>
+        <v>0.003091132674948427</v>
       </c>
       <c r="AX8" t="n">
         <v>5.447312190733356e-05</v>
@@ -4171,7 +4171,7 @@
         <v>0.1087492052643291</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.957783641161672e-05</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
         <v>0.007369580362265382</v>
@@ -4189,7 +4189,7 @@
         <v>0.003941483154049114</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001318156651741281</v>
+        <v>0.00153142396903154</v>
       </c>
       <c r="BG8" t="n">
         <v>0.0006579216644262615</v>
@@ -4201,7 +4201,7 @@
         <v>0.1905694153237517</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002331053793549046</v>
+        <v>0.002266719940988404</v>
       </c>
       <c r="BK8" t="n">
         <v>0.1143110126163887</v>
@@ -4240,7 +4240,7 @@
         <v>0.03101370355834638</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0002129494230218965</v>
+        <v>0.0002525272594335048</v>
       </c>
       <c r="BX8" t="n">
         <v>0.01157141911444834</v>
@@ -4255,7 +4255,7 @@
         <v>0.002956185480565707</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.005151349729455568</v>
+        <v>0.005188186664622558</v>
       </c>
       <c r="CC8" t="n">
         <v>0.007460125806041754</v>
@@ -4267,7 +4267,7 @@
         <v>0.003668020530701888</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0006947228160816914</v>
+        <v>0.001462996632501642</v>
       </c>
       <c r="CG8" t="n">
         <v>0.5313250115848007</v>
@@ -4279,7 +4279,7 @@
         <v>0.3985310236235365</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0002525272594335048</v>
+        <v>0.0002129494230218965</v>
       </c>
       <c r="CK8" t="n">
         <v>0.002745499978025706</v>
@@ -4306,7 +4306,7 @@
         <v>0.02464404088250085</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.4112385729611511</v>
+        <v>0.4113045360218371</v>
       </c>
       <c r="CT8" t="n">
         <v>0.08643268699238847</v>
@@ -4345,7 +4345,7 @@
         <v>0.1156756072874494</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.4112385729611511</v>
+        <v>0.4112121877368767</v>
       </c>
       <c r="DG8" t="n">
         <v>0.01261565957274452</v>
@@ -4360,7 +4360,7 @@
         <v>0.001013299788889976</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001613567166683819</v>
+        <v>0.001639952390958224</v>
       </c>
       <c r="DL8" t="n">
         <v>9.349004371719538e-05</v>
@@ -4372,7 +4372,7 @@
         <v>0.001871612185480631</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.01632956446748737</v>
+        <v>0.01645459398000277</v>
       </c>
       <c r="DP8" t="n">
         <v>0.002929990435322094</v>
@@ -4426,7 +4426,7 @@
         <v>0.0003711102529145388</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0003833961955663712</v>
+        <v>0.0002662835735065261</v>
       </c>
       <c r="EH8" t="n">
         <v>0.0005050761060803322</v>
@@ -4435,13 +4435,13 @@
         <v>0.009205488716063619</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0008296496223709343</v>
+        <v>0.001265005822898643</v>
       </c>
       <c r="EK8" t="n">
         <v>0.001112429407635884</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>3.957783641160839e-05</v>
       </c>
       <c r="EM8" t="n">
         <v>8.012820512820484e-05</v>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0004397325959001386</v>
+        <v>0.0006282694311941228</v>
       </c>
       <c r="ER8" t="n">
         <v>4.008551576697162e-05</v>
@@ -4465,7 +4465,7 @@
         <v>0.0007185633939730485</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0008952826958852022</v>
+        <v>0.0005404222176948303</v>
       </c>
       <c r="EU8" t="n">
         <v>0.00265119846139174</v>
@@ -4514,7 +4514,7 @@
         <v>0.0279960707269155</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01538461538461534</v>
+        <v>0.01533228676085815</v>
       </c>
       <c r="K9" t="n">
         <v>0.006044815007816573</v>
@@ -4706,7 +4706,7 @@
         <v>0.04002946954813356</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.04078313253012049</v>
+        <v>0.04084337349397591</v>
       </c>
       <c r="BW9" t="n">
         <v>0.00080171031533941</v>
@@ -4727,7 +4727,7 @@
         <v>0.02949452840020845</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.04036144578313253</v>
+        <v>0.04042168674698796</v>
       </c>
       <c r="CD9" t="n">
         <v>0.0159979155810318</v>
@@ -4736,7 +4736,7 @@
         <v>0.008840864440078578</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002250130821559337</v>
+        <v>0.004907651715039596</v>
       </c>
       <c r="CG9" t="n">
         <v>0.5879624804585722</v>
@@ -4802,7 +4802,7 @@
         <v>0.0007387862796833899</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.06058047493403695</v>
+        <v>0.06100263852242745</v>
       </c>
       <c r="DC9" t="n">
         <v>0.4551686014372581</v>
